--- a/term2/lab11/task4_11.xlsx
+++ b/term2/lab11/task4_11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timof\Documents\Visual Studio Code\BasicsOfAlgorithmisationAndProgramming\term2\lab11\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timofejmarusko/Documents/VisualStudioCodeRepos/BasicsOfAlgorithmisationAndProgramming/term2/lab11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466641D8-B26E-4A6A-A33D-C42DA49C81E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13128F1-EBFF-544B-9AA6-29D54ECD510C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="10440" windowWidth="26010" windowHeight="10545" xr2:uid="{7160D8B7-3DE7-42EB-B79A-D65F57C714A2}"/>
+    <workbookView xWindow="17340" yWindow="920" windowWidth="17060" windowHeight="9800" xr2:uid="{7160D8B7-3DE7-42EB-B79A-D65F57C714A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -226,28 +226,28 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>20</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.001999999999999</c:v>
+                  <c:v>21.021999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.001000000000001</c:v>
+                  <c:v>21.821000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20.077999999999999</c:v>
+                  <c:v>22.878</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.7362</c:v>
+                  <c:v>22.891999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.337</c:v>
+                  <c:v>24.637</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.190000000000001</c:v>
+                  <c:v>24.99</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>21.91</c:v>
+                  <c:v>25.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1354,13 +1354,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B25E462-662D-40CD-8EAB-8663B36CF6AF}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1368,79 +1368,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>100</v>
       </c>
       <c r="B2" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>500</v>
       </c>
       <c r="B3" s="1">
-        <v>20.001999999999999</v>
+        <v>21.021999999999998</v>
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1000</v>
       </c>
       <c r="B4" s="1">
-        <v>25.001000000000001</v>
+        <v>21.821000000000002</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>5000</v>
       </c>
       <c r="B5" s="1">
-        <v>20.077999999999999</v>
+        <v>22.878</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>10000</v>
       </c>
       <c r="B6" s="1">
-        <v>20.7362</v>
+        <v>22.891999999999999</v>
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>50000</v>
       </c>
       <c r="B7" s="1">
-        <v>20.337</v>
+        <v>24.637</v>
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>100000</v>
       </c>
       <c r="B8" s="1">
-        <v>20.190000000000001</v>
+        <v>24.99</v>
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>500000</v>
       </c>
       <c r="B9" s="1">
-        <v>21.91</v>
+        <v>25.3</v>
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
